--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-device.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-device.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Compliant Device</t>
+    <t>EU AI System Device</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A Device profile representing an AI system, fulfilling EU AI Act metadata requirements.</t>
+    <t>A Device profile representing an AI system or software component, including system identification, versioning, intended purpose, and selected regulatory documentation metadata.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -483,8 +483,7 @@
     <t>Model Card Reference</t>
   </si>
   <si>
-    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed
- documentation, intended purpose, and risk assessments.</t>
+    <t>A reference to the DocumentReference resource that acts as the Model Card, containing detailed documentation, intended purpose, and risk assessments.</t>
   </si>
   <si>
     <t>Device.modifierExtension</t>
